--- a/dist-client/sample_schedule.xlsx
+++ b/dist-client/sample_schedule.xlsx
@@ -827,10 +827,10 @@
         <v>Client A</v>
       </c>
       <c r="F2" t="str">
-        <v>2025-05-05T09:00:00</v>
+        <v>2026-05-04T09:00:00</v>
       </c>
       <c r="G2" t="str">
-        <v>2025-05-05T12:00:00</v>
+        <v>2026-05-04T12:00:00</v>
       </c>
       <c r="H2" t="str">
         <v>FALSE</v>
@@ -865,10 +865,10 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2025-05-06T14:00:00</v>
+        <v>2026-05-05T14:00:00</v>
       </c>
       <c r="G3" t="str">
-        <v>2025-05-06T15:00:00</v>
+        <v>2026-05-05T15:00:00</v>
       </c>
       <c r="H3" t="str">
         <v>FALSE</v>
@@ -903,10 +903,10 @@
         <v>Client A</v>
       </c>
       <c r="F4" t="str">
-        <v>2025-05-09T16:00:00</v>
+        <v>2026-05-08T16:00:00</v>
       </c>
       <c r="G4" t="str">
-        <v>2025-05-09T17:30:00</v>
+        <v>2026-05-08T17:30:00</v>
       </c>
       <c r="H4" t="str">
         <v>TRUE</v>
